--- a/Paintshop_Schedule_September.xlsx
+++ b/Paintshop_Schedule_September.xlsx
@@ -488,12 +488,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -506,19 +506,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>8.333333333333334</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>8.333333333333334</v>
+        <v>9</v>
       </c>
       <c r="H2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -575,28 +575,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>36</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>9</v>
-      </c>
-      <c r="G4" t="n">
-        <v>9</v>
-      </c>
-      <c r="H4" t="n">
-        <v>14</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>8</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -605,37 +605,37 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>35.5</v>
       </c>
       <c r="F5" t="n">
-        <v>7.083333333333333</v>
+        <v>12.5</v>
       </c>
       <c r="G5" t="n">
-        <v>7.083333333333333</v>
+        <v>48</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -644,7 +644,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -653,76 +653,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="G6" t="n">
-        <v>49.5</v>
+        <v>57.5</v>
       </c>
       <c r="H6" t="n">
-        <v>36</v>
+        <v>69</v>
       </c>
       <c r="I6" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>121.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>73</v>
+      </c>
+      <c r="H7" t="n">
+        <v>70</v>
+      </c>
+      <c r="I7" t="n">
         <v>3</v>
       </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>30.55555555555556</v>
-      </c>
-      <c r="F7" t="n">
-        <v>8.888888888888889</v>
-      </c>
-      <c r="G7" t="n">
-        <v>39.44444444444444</v>
-      </c>
-      <c r="H7" t="n">
-        <v>31</v>
-      </c>
-      <c r="I7" t="n">
-        <v>8.444444444444443</v>
-      </c>
       <c r="J7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>92.88888888888887</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -731,115 +731,115 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="H8" t="n">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>49.44444444444444</v>
+        <v>84</v>
       </c>
       <c r="F9" t="n">
-        <v>11.66666666666667</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>61.11111111111111</v>
+        <v>91</v>
       </c>
       <c r="H9" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="I9" t="n">
-        <v>23.11111111111111</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>300.4444444444444</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>37.66666666666666</v>
+        <v>92</v>
       </c>
       <c r="F10" t="n">
-        <v>7.916666666666667</v>
+        <v>9.5</v>
       </c>
       <c r="G10" t="n">
-        <v>45.58333333333333</v>
+        <v>101.5</v>
       </c>
       <c r="H10" t="n">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="I10" t="n">
-        <v>13.58333333333333</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K10" t="n">
-        <v>95.0833333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -848,37 +848,37 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>49.58333333333333</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="G11" t="n">
-        <v>54.58333333333333</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="H11" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="I11" t="n">
-        <v>11.58333333333333</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K11" t="n">
-        <v>115.8333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -890,73 +890,73 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>17.08333333333333</v>
+        <v>7.083333333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>9.583333333333334</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>26.66666666666666</v>
+        <v>15</v>
       </c>
       <c r="H12" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I12" t="n">
-        <v>6.666666666666664</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K12" t="n">
-        <v>59.99999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>14.33333333333333</v>
+        <v>19</v>
       </c>
       <c r="F13" t="n">
-        <v>12.22222222222222</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="G13" t="n">
-        <v>26.55555555555556</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="H13" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="I13" t="n">
-        <v>8.555555555555557</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>51.33333333333334</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -965,115 +965,115 @@
         </is>
       </c>
       <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
         <v>5</v>
       </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
       <c r="E14" t="n">
-        <v>54.58333333333333</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="F14" t="n">
-        <v>4.583333333333333</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G14" t="n">
-        <v>59.16666666666666</v>
+        <v>39.41666666666666</v>
       </c>
       <c r="H14" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="I14" t="n">
-        <v>10.16666666666666</v>
+        <v>19.41666666666666</v>
       </c>
       <c r="J14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K14" t="n">
-        <v>111.8333333333333</v>
+        <v>174.75</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>49.5</v>
+        <v>41.41666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>62</v>
+        <v>46.41666666666666</v>
       </c>
       <c r="H15" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>3.416666666666664</v>
       </c>
       <c r="J15" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>196</v>
+        <v>34.16666666666664</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>62.11111111111111</v>
+        <v>46.41666666666666</v>
       </c>
       <c r="F16" t="n">
-        <v>13.33333333333333</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="G16" t="n">
-        <v>75.44444444444444</v>
+        <v>51</v>
       </c>
       <c r="H16" t="n">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="I16" t="n">
-        <v>9.444444444444443</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K16" t="n">
-        <v>84.99999999999999</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1085,112 +1085,112 @@
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>70.91666666666666</v>
+        <v>51</v>
       </c>
       <c r="F17" t="n">
-        <v>6.666666666666667</v>
+        <v>8.75</v>
       </c>
       <c r="G17" t="n">
-        <v>77.58333333333333</v>
+        <v>59.75</v>
       </c>
       <c r="H17" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I17" t="n">
-        <v>14.58333333333333</v>
+        <v>6.75</v>
       </c>
       <c r="J17" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>116.6666666666666</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>98</v>
+        <v>62.75</v>
       </c>
       <c r="F18" t="n">
-        <v>7</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G18" t="n">
-        <v>105</v>
+        <v>69.41666666666667</v>
       </c>
       <c r="H18" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>6.416666666666671</v>
       </c>
       <c r="J18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K18" t="n">
-        <v>240</v>
+        <v>51.33333333333337</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>75.44444444444444</v>
+        <v>69.41666666666667</v>
       </c>
       <c r="F19" t="n">
-        <v>11.66666666666667</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G19" t="n">
-        <v>87.11111111111111</v>
+        <v>77.75</v>
       </c>
       <c r="H19" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="I19" t="n">
-        <v>9.111111111111114</v>
+        <v>3.75</v>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>91.11111111111114</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1199,343 +1199,343 @@
         </is>
       </c>
       <c r="C20" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>77.75</v>
+      </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>82.75</v>
+      </c>
+      <c r="H20" t="n">
+        <v>78</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J20" t="n">
         <v>8</v>
       </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>77.58333333333333</v>
-      </c>
-      <c r="F20" t="n">
-        <v>8.333333333333334</v>
-      </c>
-      <c r="G20" t="n">
-        <v>85.91666666666666</v>
-      </c>
-      <c r="H20" t="n">
-        <v>74</v>
-      </c>
-      <c r="I20" t="n">
-        <v>11.91666666666666</v>
-      </c>
-      <c r="J20" t="n">
-        <v>15</v>
-      </c>
       <c r="K20" t="n">
-        <v>178.7499999999999</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>79.5</v>
+        <v>86.75</v>
       </c>
       <c r="F21" t="n">
-        <v>7.5</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G21" t="n">
-        <v>87</v>
+        <v>92.16666666666667</v>
       </c>
       <c r="H21" t="n">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>6.166666666666671</v>
       </c>
       <c r="J21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K21" t="n">
-        <v>204</v>
+        <v>61.66666666666671</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>63</v>
+        <v>95.16666666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="G22" t="n">
-        <v>71.5</v>
+        <v>102.6666666666667</v>
       </c>
       <c r="H22" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K22" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>94.91666666666666</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>5.416666666666667</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>100.3333333333333</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="H23" t="n">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="I23" t="n">
-        <v>14.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>10</v>
       </c>
       <c r="K23" t="n">
-        <v>143.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>103.3333333333333</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="F24" t="n">
-        <v>7.5</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="G24" t="n">
-        <v>110.8333333333333</v>
+        <v>20.22222222222222</v>
       </c>
       <c r="H24" t="n">
-        <v>104</v>
+        <v>31</v>
       </c>
       <c r="I24" t="n">
-        <v>6.833333333333329</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K24" t="n">
-        <v>61.49999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD24</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
         <v>10</v>
       </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
       <c r="E25" t="n">
-        <v>106</v>
+        <v>30.22222222222222</v>
       </c>
       <c r="F25" t="n">
-        <v>9.5</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G25" t="n">
-        <v>115.5</v>
+        <v>41.88888888888889</v>
       </c>
       <c r="H25" t="n">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>3.888888888888886</v>
       </c>
       <c r="J25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K25" t="n">
-        <v>30</v>
+        <v>50.55555555555551</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>42.88888888888889</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12.22222222222222</v>
+      </c>
+      <c r="G26" t="n">
+        <v>55.11111111111111</v>
+      </c>
+      <c r="H26" t="n">
+        <v>18</v>
+      </c>
+      <c r="I26" t="n">
+        <v>37.11111111111111</v>
+      </c>
+      <c r="J26" t="n">
         <v>6</v>
       </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>59.16666666666666</v>
-      </c>
-      <c r="F26" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="G26" t="n">
-        <v>67.91666666666666</v>
-      </c>
-      <c r="H26" t="n">
-        <v>53</v>
-      </c>
-      <c r="I26" t="n">
-        <v>14.91666666666666</v>
-      </c>
-      <c r="J26" t="n">
-        <v>14</v>
-      </c>
       <c r="K26" t="n">
-        <v>208.8333333333332</v>
+        <v>222.6666666666666</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>87</v>
+        <v>55.11111111111111</v>
       </c>
       <c r="F27" t="n">
-        <v>11</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="G27" t="n">
-        <v>98</v>
+        <v>68.44444444444444</v>
       </c>
       <c r="H27" t="n">
-        <v>81</v>
+        <v>66</v>
       </c>
       <c r="I27" t="n">
-        <v>17</v>
+        <v>2.444444444444443</v>
       </c>
       <c r="J27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K27" t="n">
-        <v>187</v>
+        <v>21.99999999999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>85.91666666666666</v>
+        <v>68.44444444444444</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G28" t="n">
-        <v>90.91666666666666</v>
+        <v>80.11111111111111</v>
       </c>
       <c r="H28" t="n">
         <v>78</v>
       </c>
       <c r="I28" t="n">
-        <v>12.91666666666666</v>
+        <v>2.111111111111114</v>
       </c>
       <c r="J28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K28" t="n">
-        <v>103.3333333333333</v>
+        <v>21.11111111111114</v>
       </c>
     </row>
     <row r="29">
@@ -1556,25 +1556,25 @@
         <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>92.11111111111111</v>
+        <v>85.11111111111111</v>
       </c>
       <c r="F29" t="n">
         <v>12.77777777777778</v>
       </c>
       <c r="G29" t="n">
-        <v>104.8888888888889</v>
+        <v>97.88888888888889</v>
       </c>
       <c r="H29" t="n">
         <v>82</v>
       </c>
       <c r="I29" t="n">
-        <v>22.88888888888889</v>
+        <v>15.88888888888889</v>
       </c>
       <c r="J29" t="n">
         <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>137.3333333333333</v>
+        <v>95.33333333333331</v>
       </c>
     </row>
   </sheetData>

--- a/Paintshop_Schedule_September.xlsx
+++ b/Paintshop_Schedule_September.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Schedule" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Machine</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SeqNo</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Start</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>End</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Deadline</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Tardiness</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Penalty</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>

--- a/Paintshop_Schedule_September.xlsx
+++ b/Paintshop_Schedule_September.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -527,34 +527,34 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -566,34 +566,34 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F4" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="G4" t="n">
-        <v>35.5</v>
+        <v>37</v>
       </c>
       <c r="H4" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -608,31 +608,31 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>35.5</v>
+        <v>37</v>
       </c>
       <c r="F5" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="G5" t="n">
-        <v>48</v>
+        <v>43.5</v>
       </c>
       <c r="H5" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -644,28 +644,28 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>49</v>
+        <v>43.5</v>
       </c>
       <c r="F6" t="n">
-        <v>8.5</v>
+        <v>12.5</v>
       </c>
       <c r="G6" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="H6" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7">
@@ -683,28 +683,28 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>65.5</v>
+        <v>56</v>
       </c>
       <c r="F7" t="n">
         <v>7.5</v>
       </c>
       <c r="G7" t="n">
-        <v>73</v>
+        <v>63.5</v>
       </c>
       <c r="H7" t="n">
         <v>70</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -725,25 +725,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>63.5</v>
       </c>
       <c r="F8" t="n">
         <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>84</v>
+        <v>74.5</v>
       </c>
       <c r="H8" t="n">
         <v>81</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -764,25 +764,25 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>84</v>
+        <v>74.5</v>
       </c>
       <c r="F9" t="n">
         <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>91</v>
+        <v>81.5</v>
       </c>
       <c r="H9" t="n">
         <v>85</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -803,13 +803,13 @@
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>92</v>
+        <v>82.5</v>
       </c>
       <c r="F10" t="n">
         <v>9.5</v>
       </c>
       <c r="G10" t="n">
-        <v>101.5</v>
+        <v>92</v>
       </c>
       <c r="H10" t="n">
         <v>113</v>
@@ -983,7 +983,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1001,28 +1001,28 @@
         <v>41.41666666666666</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4.583333333333333</v>
       </c>
       <c r="G15" t="n">
-        <v>46.41666666666666</v>
+        <v>46</v>
       </c>
       <c r="H15" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I15" t="n">
-        <v>3.416666666666664</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" t="n">
-        <v>34.16666666666664</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1037,31 +1037,31 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>46.41666666666666</v>
+        <v>46</v>
       </c>
       <c r="F16" t="n">
-        <v>4.583333333333333</v>
+        <v>8.75</v>
       </c>
       <c r="G16" t="n">
-        <v>51</v>
+        <v>54.75</v>
       </c>
       <c r="H16" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="J16" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>22</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1073,34 +1073,34 @@
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>51</v>
+        <v>57.75</v>
       </c>
       <c r="F17" t="n">
-        <v>8.75</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G17" t="n">
-        <v>59.75</v>
+        <v>64.41666666666667</v>
       </c>
       <c r="H17" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="I17" t="n">
-        <v>6.75</v>
+        <v>1.416666666666671</v>
       </c>
       <c r="J17" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
-        <v>94.5</v>
+        <v>11.33333333333337</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1112,34 +1112,34 @@
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>62.75</v>
+        <v>64.41666666666667</v>
       </c>
       <c r="F18" t="n">
-        <v>6.666666666666667</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G18" t="n">
-        <v>69.41666666666667</v>
+        <v>72.75</v>
       </c>
       <c r="H18" t="n">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="I18" t="n">
-        <v>6.416666666666671</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>51.33333333333337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1154,31 +1154,31 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>69.41666666666667</v>
+        <v>72.75</v>
       </c>
       <c r="F19" t="n">
-        <v>8.333333333333334</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
         <v>77.75</v>
       </c>
       <c r="H19" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="I19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K19" t="n">
-        <v>56.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1190,34 +1190,34 @@
         <v>10</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
-        <v>77.75</v>
+        <v>81.75</v>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G20" t="n">
-        <v>82.75</v>
+        <v>87.16666666666667</v>
       </c>
       <c r="H20" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I20" t="n">
-        <v>4.75</v>
+        <v>1.166666666666671</v>
       </c>
       <c r="J20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K20" t="n">
-        <v>38</v>
+        <v>11.66666666666671</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1229,64 +1229,64 @@
         <v>11</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>86.75</v>
+        <v>90.16666666666667</v>
       </c>
       <c r="F21" t="n">
-        <v>5.416666666666667</v>
+        <v>7.5</v>
       </c>
       <c r="G21" t="n">
-        <v>92.16666666666667</v>
+        <v>97.66666666666667</v>
       </c>
       <c r="H21" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="I21" t="n">
-        <v>6.166666666666671</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K21" t="n">
-        <v>61.66666666666671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>95.16666666666667</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>7.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G22" t="n">
-        <v>102.6666666666667</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="H22" t="n">
-        <v>104</v>
+        <v>17</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1295,7 +1295,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1304,22 +1304,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="F23" t="n">
-        <v>8.333333333333334</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G23" t="n">
-        <v>8.333333333333334</v>
+        <v>15</v>
       </c>
       <c r="H23" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1343,28 +1343,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E24" t="n">
-        <v>11.33333333333333</v>
+        <v>20</v>
       </c>
       <c r="F24" t="n">
-        <v>8.888888888888889</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="G24" t="n">
-        <v>20.22222222222222</v>
+        <v>31.66666666666666</v>
       </c>
       <c r="H24" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1373,7 +1373,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1382,37 +1382,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>30.22222222222222</v>
+        <v>32.66666666666666</v>
       </c>
       <c r="F25" t="n">
-        <v>11.66666666666667</v>
+        <v>12.22222222222222</v>
       </c>
       <c r="G25" t="n">
-        <v>41.88888888888889</v>
+        <v>44.88888888888889</v>
       </c>
       <c r="H25" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I25" t="n">
-        <v>3.888888888888886</v>
+        <v>26.88888888888889</v>
       </c>
       <c r="J25" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K25" t="n">
-        <v>50.55555555555551</v>
+        <v>161.3333333333333</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1421,37 +1421,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>42.88888888888889</v>
+        <v>44.88888888888889</v>
       </c>
       <c r="F26" t="n">
-        <v>12.22222222222222</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="G26" t="n">
-        <v>55.11111111111111</v>
+        <v>58.22222222222222</v>
       </c>
       <c r="H26" t="n">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="I26" t="n">
-        <v>37.11111111111111</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K26" t="n">
-        <v>222.6666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1460,31 +1460,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>55.11111111111111</v>
+        <v>58.22222222222222</v>
       </c>
       <c r="F27" t="n">
-        <v>13.33333333333333</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="G27" t="n">
-        <v>68.44444444444444</v>
+        <v>67.66666666666667</v>
       </c>
       <c r="H27" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I27" t="n">
-        <v>2.444444444444443</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>21.99999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1499,31 +1499,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>68.44444444444444</v>
+        <v>67.66666666666667</v>
       </c>
       <c r="F28" t="n">
         <v>11.66666666666667</v>
       </c>
       <c r="G28" t="n">
-        <v>80.11111111111111</v>
+        <v>79.33333333333334</v>
       </c>
       <c r="H28" t="n">
         <v>78</v>
       </c>
       <c r="I28" t="n">
-        <v>2.111111111111114</v>
+        <v>1.333333333333343</v>
       </c>
       <c r="J28" t="n">
         <v>10</v>
       </c>
       <c r="K28" t="n">
-        <v>21.11111111111114</v>
+        <v>13.33333333333343</v>
       </c>
     </row>
     <row r="29">
@@ -1538,31 +1538,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D29" t="n">
         <v>5</v>
       </c>
       <c r="E29" t="n">
-        <v>85.11111111111111</v>
+        <v>84.33333333333334</v>
       </c>
       <c r="F29" t="n">
         <v>12.77777777777778</v>
       </c>
       <c r="G29" t="n">
-        <v>97.88888888888889</v>
+        <v>97.11111111111111</v>
       </c>
       <c r="H29" t="n">
         <v>82</v>
       </c>
       <c r="I29" t="n">
-        <v>15.88888888888889</v>
+        <v>15.11111111111111</v>
       </c>
       <c r="J29" t="n">
         <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>95.33333333333331</v>
+        <v>90.66666666666669</v>
       </c>
     </row>
   </sheetData>
